--- a/Test_2026_01_28/input.xlsx
+++ b/Test_2026_01_28/input.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hans\Desktop\PyORCHESTRA\Test_2026_01_28\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1367E0C-7242-4611-88E5-5912D0141892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="3470" yWindow="2330" windowWidth="21250" windowHeight="13100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,16 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+  <si>
+    <t xml:space="preserve">pH                       </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +344,1628 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C3:D204"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>1.06</v>
+      </c>
+      <c r="D5">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D6">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>1.18</v>
+      </c>
+      <c r="D7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <v>1.24</v>
+      </c>
+      <c r="D8">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <v>1.3</v>
+      </c>
+      <c r="D9">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <v>1.36</v>
+      </c>
+      <c r="D10">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C11">
+        <v>1.42</v>
+      </c>
+      <c r="D11">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C12">
+        <v>1.48</v>
+      </c>
+      <c r="D12">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C13">
+        <v>1.54</v>
+      </c>
+      <c r="D13">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <v>1.6</v>
+      </c>
+      <c r="D14">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C15">
+        <v>1.66</v>
+      </c>
+      <c r="D15">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C16">
+        <v>1.72</v>
+      </c>
+      <c r="D16">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <v>1.78</v>
+      </c>
+      <c r="D17">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <v>1.84</v>
+      </c>
+      <c r="D18">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <v>1.9</v>
+      </c>
+      <c r="D19">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <v>1.96</v>
+      </c>
+      <c r="D20">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <v>2.02</v>
+      </c>
+      <c r="D21">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C22">
+        <v>2.08</v>
+      </c>
+      <c r="D22">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C23">
+        <v>2.14</v>
+      </c>
+      <c r="D23">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D24">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="D25">
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C26">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="D26">
+        <v>2.3199999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <v>2.38</v>
+      </c>
+      <c r="D27">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C28">
+        <v>2.44</v>
+      </c>
+      <c r="D28">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C29">
+        <v>2.5</v>
+      </c>
+      <c r="D29">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C30">
+        <v>2.56</v>
+      </c>
+      <c r="D30">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C31">
+        <v>2.62</v>
+      </c>
+      <c r="D31">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C32">
+        <v>2.68</v>
+      </c>
+      <c r="D32">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C33">
+        <v>2.74</v>
+      </c>
+      <c r="D33">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C34">
+        <v>2.8</v>
+      </c>
+      <c r="D34">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C35">
+        <v>2.86</v>
+      </c>
+      <c r="D35">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C36">
+        <v>2.92</v>
+      </c>
+      <c r="D36">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C37">
+        <v>2.98</v>
+      </c>
+      <c r="D37">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C38">
+        <v>3.04</v>
+      </c>
+      <c r="D38">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C39">
+        <v>3.1</v>
+      </c>
+      <c r="D39">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C40">
+        <v>3.16</v>
+      </c>
+      <c r="D40">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C41">
+        <v>3.22</v>
+      </c>
+      <c r="D41">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C42">
+        <v>3.28</v>
+      </c>
+      <c r="D42">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C43">
+        <v>3.34</v>
+      </c>
+      <c r="D43">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C44">
+        <v>3.4</v>
+      </c>
+      <c r="D44">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C45">
+        <v>3.46</v>
+      </c>
+      <c r="D45">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C46">
+        <v>3.52</v>
+      </c>
+      <c r="D46">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C47">
+        <v>3.58</v>
+      </c>
+      <c r="D47">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C48">
+        <v>3.64</v>
+      </c>
+      <c r="D48">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C49">
+        <v>3.7</v>
+      </c>
+      <c r="D49">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C50">
+        <v>3.76</v>
+      </c>
+      <c r="D50">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C51">
+        <v>3.82</v>
+      </c>
+      <c r="D51">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C52">
+        <v>3.88</v>
+      </c>
+      <c r="D52">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C53">
+        <v>3.94</v>
+      </c>
+      <c r="D53">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C55">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="D55">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C56">
+        <v>4.12</v>
+      </c>
+      <c r="D56">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C57">
+        <v>4.18</v>
+      </c>
+      <c r="D57">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C58">
+        <v>4.24</v>
+      </c>
+      <c r="D58">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C59">
+        <v>4.3</v>
+      </c>
+      <c r="D59">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C60">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="D60">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C61">
+        <v>4.42</v>
+      </c>
+      <c r="D61">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C62">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="D62">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C63">
+        <v>4.54</v>
+      </c>
+      <c r="D63">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C64">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D64">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C65">
+        <v>4.66</v>
+      </c>
+      <c r="D65">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C66">
+        <v>4.72</v>
+      </c>
+      <c r="D66">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C67">
+        <v>4.78</v>
+      </c>
+      <c r="D67">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C68">
+        <v>4.84</v>
+      </c>
+      <c r="D68">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C69">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D69">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C70">
+        <v>4.96</v>
+      </c>
+      <c r="D70">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C71">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="D71">
+        <v>5.0199999999999996</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C72">
+        <v>5.08</v>
+      </c>
+      <c r="D72">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C73">
+        <v>5.14</v>
+      </c>
+      <c r="D73">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C74">
+        <v>5.2</v>
+      </c>
+      <c r="D74">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C75">
+        <v>5.26</v>
+      </c>
+      <c r="D75">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C76">
+        <v>5.32</v>
+      </c>
+      <c r="D76">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C77">
+        <v>5.38</v>
+      </c>
+      <c r="D77">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C78">
+        <v>5.44</v>
+      </c>
+      <c r="D78">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C79">
+        <v>5.5</v>
+      </c>
+      <c r="D79">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C80">
+        <v>5.56</v>
+      </c>
+      <c r="D80">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C81">
+        <v>5.62</v>
+      </c>
+      <c r="D81">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C82">
+        <v>5.68</v>
+      </c>
+      <c r="D82">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C83">
+        <v>5.74</v>
+      </c>
+      <c r="D83">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C84">
+        <v>5.8</v>
+      </c>
+      <c r="D84">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C85">
+        <v>5.86</v>
+      </c>
+      <c r="D85">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C86">
+        <v>5.92</v>
+      </c>
+      <c r="D86">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C87">
+        <v>5.98</v>
+      </c>
+      <c r="D87">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C88">
+        <v>6.04</v>
+      </c>
+      <c r="D88">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C89">
+        <v>6.1</v>
+      </c>
+      <c r="D89">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C90">
+        <v>6.16</v>
+      </c>
+      <c r="D90">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C91">
+        <v>6.22</v>
+      </c>
+      <c r="D91">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C92">
+        <v>6.28</v>
+      </c>
+      <c r="D92">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C93">
+        <v>6.34</v>
+      </c>
+      <c r="D93">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C94">
+        <v>6.4</v>
+      </c>
+      <c r="D94">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C95">
+        <v>6.46</v>
+      </c>
+      <c r="D95">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C96">
+        <v>6.52</v>
+      </c>
+      <c r="D96">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C97">
+        <v>6.58</v>
+      </c>
+      <c r="D97">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C98">
+        <v>6.64</v>
+      </c>
+      <c r="D98">
+        <v>6.64</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C99">
+        <v>6.7</v>
+      </c>
+      <c r="D99">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C100">
+        <v>6.76</v>
+      </c>
+      <c r="D100">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C101">
+        <v>6.82</v>
+      </c>
+      <c r="D101">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C102">
+        <v>6.88</v>
+      </c>
+      <c r="D102">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C103">
+        <v>6.94</v>
+      </c>
+      <c r="D103">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C104">
+        <v>7</v>
+      </c>
+      <c r="D104">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C105">
+        <v>7.06</v>
+      </c>
+      <c r="D105">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C106">
+        <v>7.12</v>
+      </c>
+      <c r="D106">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C107">
+        <v>7.18</v>
+      </c>
+      <c r="D107">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C108">
+        <v>7.24</v>
+      </c>
+      <c r="D108">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C109">
+        <v>7.3</v>
+      </c>
+      <c r="D109">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C110">
+        <v>7.36</v>
+      </c>
+      <c r="D110">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C111">
+        <v>7.42</v>
+      </c>
+      <c r="D111">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C112">
+        <v>7.48</v>
+      </c>
+      <c r="D112">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="113" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C113">
+        <v>7.54</v>
+      </c>
+      <c r="D113">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="114" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C114">
+        <v>7.6</v>
+      </c>
+      <c r="D114">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="115" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C115">
+        <v>7.66</v>
+      </c>
+      <c r="D115">
+        <v>7.66</v>
+      </c>
+    </row>
+    <row r="116" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C116">
+        <v>7.72</v>
+      </c>
+      <c r="D116">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="117" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C117">
+        <v>7.78</v>
+      </c>
+      <c r="D117">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="118" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C118">
+        <v>7.84</v>
+      </c>
+      <c r="D118">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="119" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C119">
+        <v>7.9</v>
+      </c>
+      <c r="D119">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="120" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C120">
+        <v>7.96</v>
+      </c>
+      <c r="D120">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="121" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C121">
+        <v>8.02</v>
+      </c>
+      <c r="D121">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="122" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C122">
+        <v>8.08</v>
+      </c>
+      <c r="D122">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="123" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C123">
+        <v>8.14</v>
+      </c>
+      <c r="D123">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="124" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C124">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D124">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="125" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C125">
+        <v>8.26</v>
+      </c>
+      <c r="D125">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="126" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C126">
+        <v>8.32</v>
+      </c>
+      <c r="D126">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="127" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C127">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="D127">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="128" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C128">
+        <v>8.44</v>
+      </c>
+      <c r="D128">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="129" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C129">
+        <v>8.5</v>
+      </c>
+      <c r="D129">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="130" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C130">
+        <v>8.56</v>
+      </c>
+      <c r="D130">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="131" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C131">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="D131">
+        <v>8.6199999999999992</v>
+      </c>
+    </row>
+    <row r="132" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C132">
+        <v>8.68</v>
+      </c>
+      <c r="D132">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="133" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C133">
+        <v>8.74</v>
+      </c>
+      <c r="D133">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="134" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C134">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D134">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="135" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C135">
+        <v>8.86</v>
+      </c>
+      <c r="D135">
+        <v>8.86</v>
+      </c>
+    </row>
+    <row r="136" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C136">
+        <v>8.92</v>
+      </c>
+      <c r="D136">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="137" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C137">
+        <v>8.98</v>
+      </c>
+      <c r="D137">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="138" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C138">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="D138">
+        <v>9.0399999999999991</v>
+      </c>
+    </row>
+    <row r="139" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C139">
+        <v>9.1</v>
+      </c>
+      <c r="D139">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="140" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C140">
+        <v>9.16</v>
+      </c>
+      <c r="D140">
+        <v>9.16</v>
+      </c>
+    </row>
+    <row r="141" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C141">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="D141">
+        <v>9.2200000000000006</v>
+      </c>
+    </row>
+    <row r="142" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C142">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="D142">
+        <v>9.2799999999999994</v>
+      </c>
+    </row>
+    <row r="143" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C143">
+        <v>9.34</v>
+      </c>
+      <c r="D143">
+        <v>9.34</v>
+      </c>
+    </row>
+    <row r="144" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C144">
+        <v>9.4</v>
+      </c>
+      <c r="D144">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="145" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C145">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="D145">
+        <v>9.4600000000000009</v>
+      </c>
+    </row>
+    <row r="146" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C146">
+        <v>9.52</v>
+      </c>
+      <c r="D146">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="147" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C147">
+        <v>9.58</v>
+      </c>
+      <c r="D147">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="148" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C148">
+        <v>9.64</v>
+      </c>
+      <c r="D148">
+        <v>9.64</v>
+      </c>
+    </row>
+    <row r="149" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C149">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D149">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="150" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C150">
+        <v>9.76</v>
+      </c>
+      <c r="D150">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="151" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C151">
+        <v>9.82</v>
+      </c>
+      <c r="D151">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="152" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C152">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="D152">
+        <v>9.8800000000000008</v>
+      </c>
+    </row>
+    <row r="153" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C153">
+        <v>9.94</v>
+      </c>
+      <c r="D153">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="154" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C154">
+        <v>10</v>
+      </c>
+      <c r="D154">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C155">
+        <v>10.06</v>
+      </c>
+      <c r="D155">
+        <v>10.06</v>
+      </c>
+    </row>
+    <row r="156" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C156">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="D156">
+        <v>10.119999999999999</v>
+      </c>
+    </row>
+    <row r="157" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C157">
+        <v>10.18</v>
+      </c>
+      <c r="D157">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="158" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C158">
+        <v>10.24</v>
+      </c>
+      <c r="D158">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="159" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C159">
+        <v>10.3</v>
+      </c>
+      <c r="D159">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="160" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C160">
+        <v>10.36</v>
+      </c>
+      <c r="D160">
+        <v>10.36</v>
+      </c>
+    </row>
+    <row r="161" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C161">
+        <v>10.42</v>
+      </c>
+      <c r="D161">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="162" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C162">
+        <v>10.48</v>
+      </c>
+      <c r="D162">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="163" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C163">
+        <v>10.54</v>
+      </c>
+      <c r="D163">
+        <v>10.54</v>
+      </c>
+    </row>
+    <row r="164" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C164">
+        <v>10.6</v>
+      </c>
+      <c r="D164">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="165" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C165">
+        <v>10.66</v>
+      </c>
+      <c r="D165">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="166" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C166">
+        <v>10.72</v>
+      </c>
+      <c r="D166">
+        <v>10.72</v>
+      </c>
+    </row>
+    <row r="167" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C167">
+        <v>10.78</v>
+      </c>
+      <c r="D167">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="168" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C168">
+        <v>10.84</v>
+      </c>
+      <c r="D168">
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="169" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C169">
+        <v>10.9</v>
+      </c>
+      <c r="D169">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="170" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C170">
+        <v>10.96</v>
+      </c>
+      <c r="D170">
+        <v>10.96</v>
+      </c>
+    </row>
+    <row r="171" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C171">
+        <v>11.02</v>
+      </c>
+      <c r="D171">
+        <v>11.02</v>
+      </c>
+    </row>
+    <row r="172" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C172">
+        <v>11.08</v>
+      </c>
+      <c r="D172">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="173" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C173">
+        <v>11.14</v>
+      </c>
+      <c r="D173">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="174" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C174">
+        <v>11.2</v>
+      </c>
+      <c r="D174">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="175" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C175">
+        <v>11.26</v>
+      </c>
+      <c r="D175">
+        <v>11.26</v>
+      </c>
+    </row>
+    <row r="176" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C176">
+        <v>11.32</v>
+      </c>
+      <c r="D176">
+        <v>11.32</v>
+      </c>
+    </row>
+    <row r="177" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C177">
+        <v>11.38</v>
+      </c>
+      <c r="D177">
+        <v>11.38</v>
+      </c>
+    </row>
+    <row r="178" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C178">
+        <v>11.44</v>
+      </c>
+      <c r="D178">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="179" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C179">
+        <v>11.5</v>
+      </c>
+      <c r="D179">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="180" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C180">
+        <v>11.56</v>
+      </c>
+      <c r="D180">
+        <v>11.56</v>
+      </c>
+    </row>
+    <row r="181" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C181">
+        <v>11.62</v>
+      </c>
+      <c r="D181">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="182" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C182">
+        <v>11.68</v>
+      </c>
+      <c r="D182">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="183" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C183">
+        <v>11.74</v>
+      </c>
+      <c r="D183">
+        <v>11.74</v>
+      </c>
+    </row>
+    <row r="184" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C184">
+        <v>11.8</v>
+      </c>
+      <c r="D184">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="185" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C185">
+        <v>11.86</v>
+      </c>
+      <c r="D185">
+        <v>11.86</v>
+      </c>
+    </row>
+    <row r="186" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C186">
+        <v>11.92</v>
+      </c>
+      <c r="D186">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="187" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C187">
+        <v>11.98</v>
+      </c>
+      <c r="D187">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="188" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C188">
+        <v>12.04</v>
+      </c>
+      <c r="D188">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="189" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C189">
+        <v>12.1</v>
+      </c>
+      <c r="D189">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="190" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C190">
+        <v>12.16</v>
+      </c>
+      <c r="D190">
+        <v>12.16</v>
+      </c>
+    </row>
+    <row r="191" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C191">
+        <v>12.22</v>
+      </c>
+      <c r="D191">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="192" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C192">
+        <v>12.28</v>
+      </c>
+      <c r="D192">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="193" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C193">
+        <v>12.34</v>
+      </c>
+      <c r="D193">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="194" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C194">
+        <v>12.4</v>
+      </c>
+      <c r="D194">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="195" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C195">
+        <v>12.46</v>
+      </c>
+      <c r="D195">
+        <v>12.46</v>
+      </c>
+    </row>
+    <row r="196" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C196">
+        <v>12.52</v>
+      </c>
+      <c r="D196">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="197" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C197">
+        <v>12.58</v>
+      </c>
+      <c r="D197">
+        <v>12.58</v>
+      </c>
+    </row>
+    <row r="198" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C198">
+        <v>12.64</v>
+      </c>
+      <c r="D198">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="199" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C199">
+        <v>12.7</v>
+      </c>
+      <c r="D199">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="200" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C200">
+        <v>12.76</v>
+      </c>
+      <c r="D200">
+        <v>12.76</v>
+      </c>
+    </row>
+    <row r="201" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C201">
+        <v>12.82</v>
+      </c>
+      <c r="D201">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="202" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C202">
+        <v>12.88</v>
+      </c>
+      <c r="D202">
+        <v>12.88</v>
+      </c>
+    </row>
+    <row r="203" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C203">
+        <v>12.94</v>
+      </c>
+      <c r="D203">
+        <v>12.94</v>
+      </c>
+    </row>
+    <row r="204" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C204">
+        <v>13</v>
+      </c>
+      <c r="D204">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>